--- a/customers.xlsx
+++ b/customers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamadayuta/Desktop/python/株/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D364BA1-21E1-2A48-B35B-92497DE8F1BD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD91C98-4D30-974A-8280-23D195B49B32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2000" yWindow="7680" windowWidth="28300" windowHeight="16200" xr2:uid="{61C43985-F52B-7448-B153-E76C3CBAE039}"/>
+    <workbookView xWindow="500" yWindow="600" windowWidth="28300" windowHeight="16200" xr2:uid="{61C43985-F52B-7448-B153-E76C3CBAE039}"/>
   </bookViews>
   <sheets>
     <sheet name="customers" sheetId="1" r:id="rId1"/>
@@ -671,10 +671,10 @@
         <v>16400</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="H6">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamadayuta/Desktop/python/株/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A77584-FA27-084D-B983-D21AF180670D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B07AAF-EE5B-FE41-B56A-18A2DAFF1D34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="600" windowWidth="28300" windowHeight="16180" xr2:uid="{61C43985-F52B-7448-B153-E76C3CBAE039}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>customer_id</t>
     <phoneticPr fontId="1"/>
@@ -108,15 +108,30 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>PDRゴールドシェア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1326.T</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>9501.T</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>koko07na03@gmail.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPDRゴールドシェア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9531.T</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京ガス</t>
+    <rPh sb="0" eb="2">
+      <t>トウキョウガス</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -500,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4808F3F-3F53-6548-B3B1-1B8AA7E251C7}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -691,7 +706,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1">
         <v>45870</v>
@@ -717,10 +732,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
         <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
       </c>
       <c r="E8" s="1">
         <v>46038</v>
@@ -735,6 +750,35 @@
         <v>8</v>
       </c>
       <c r="I8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1">
+        <v>46248</v>
+      </c>
+      <c r="F9">
+        <v>6015</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -744,6 +788,7 @@
     <hyperlink ref="B2" r:id="rId1" xr:uid="{392DAADB-8A35-C041-A0E9-118813A1F762}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{46BABC43-483B-A84A-806C-382BED0043AE}"/>
     <hyperlink ref="B4:B8" r:id="rId3" display="yama01yu18@gmail.com" xr:uid="{1C6F4349-7D14-3A45-9218-4109571A9E8F}"/>
+    <hyperlink ref="B9" r:id="rId4" xr:uid="{7D92526E-C8C7-714B-A9A4-99C8E337F0A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamadayuta/Desktop/python/株/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B07AAF-EE5B-FE41-B56A-18A2DAFF1D34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204823D0-A527-EB42-B8FD-112FCC7B9A52}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="600" windowWidth="28300" windowHeight="16180" xr2:uid="{61C43985-F52B-7448-B153-E76C3CBAE039}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>customer_id</t>
     <phoneticPr fontId="1"/>
@@ -116,22 +116,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>koko07na03@gmail.com</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>SPDRゴールドシェア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9531.T</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>東京ガス</t>
-    <rPh sb="0" eb="2">
-      <t>トウキョウガス</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -515,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4808F3F-3F53-6548-B3B1-1B8AA7E251C7}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -686,10 +671,10 @@
         <v>16400</v>
       </c>
       <c r="G6">
-        <v>-50</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>-5</v>
+        <v>12</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -732,7 +717,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
@@ -750,35 +735,6 @@
         <v>8</v>
       </c>
       <c r="I8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="1">
-        <v>46248</v>
-      </c>
-      <c r="F9">
-        <v>6015</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -788,7 +744,6 @@
     <hyperlink ref="B2" r:id="rId1" xr:uid="{392DAADB-8A35-C041-A0E9-118813A1F762}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{46BABC43-483B-A84A-806C-382BED0043AE}"/>
     <hyperlink ref="B4:B8" r:id="rId3" display="yama01yu18@gmail.com" xr:uid="{1C6F4349-7D14-3A45-9218-4109571A9E8F}"/>
-    <hyperlink ref="B9" r:id="rId4" xr:uid="{7D92526E-C8C7-714B-A9A4-99C8E337F0A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
